--- a/simulation/biogas/biogas_mass_flow_data.xlsx
+++ b/simulation/biogas/biogas_mass_flow_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Propanol production\simulation\biogas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67C87E6-DBFD-41B1-9C6D-ABFB3749CACC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6129D2C-3DB1-4AA2-B08C-894893814916}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="6585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="6585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="material_streams" sheetId="1" r:id="rId1"/>
@@ -629,7 +629,7 @@
         <v>1050.9805003199999</v>
       </c>
       <c r="E4" s="18">
-        <f>D4/$D$16</f>
+        <f t="shared" ref="E4:E16" si="0">D4/$D$16</f>
         <v>8.4072281848774813E-2</v>
       </c>
       <c r="F4" s="17"/>
@@ -648,7 +648,7 @@
         <v>5364.9232006304101</v>
       </c>
       <c r="E5" s="18">
-        <f>D5/$D$16</f>
+        <f t="shared" si="0"/>
         <v>0.42916242050456593</v>
       </c>
       <c r="F5" s="17"/>
@@ -668,7 +668,7 @@
         <v>430.11153141017348</v>
       </c>
       <c r="E6" s="18">
-        <f>D6/$D$16</f>
+        <f t="shared" si="0"/>
         <v>3.4406402292063668E-2</v>
       </c>
     </row>
@@ -686,7 +686,7 @@
         <v>5861.9886311727596</v>
       </c>
       <c r="E7" s="18">
-        <f>D7/$D$16</f>
+        <f t="shared" si="0"/>
         <v>0.46892474241359761</v>
       </c>
     </row>
@@ -701,11 +701,11 @@
         <v>10</v>
       </c>
       <c r="D8" s="14">
-        <v>103.02685492433901</v>
+        <v>6.5601219350892901</v>
       </c>
       <c r="E8" s="18">
-        <f>D8/$D$16</f>
-        <v>8.2415447123467735E-3</v>
+        <f t="shared" si="0"/>
+        <v>5.247713160436659E-4</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -719,11 +719,11 @@
         <v>10</v>
       </c>
       <c r="D9" s="14">
-        <v>1754.33338664506</v>
+        <v>50.390914199658098</v>
       </c>
       <c r="E9" s="18">
-        <f>D9/$D$16</f>
-        <v>0.14033639148759799</v>
+        <f t="shared" si="0"/>
+        <v>4.0309778724925641E-3</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -737,11 +737,11 @@
         <v>11</v>
       </c>
       <c r="D10" s="14">
-        <v>1877.1641154558899</v>
+        <v>73.784757068013604</v>
       </c>
       <c r="E10" s="18">
-        <f>D10/$D$16</f>
-        <v>0.15016213007088311</v>
+        <f t="shared" si="0"/>
+        <v>5.9023482267051269E-3</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -758,7 +758,7 @@
         <v>57.122061310234798</v>
       </c>
       <c r="E11" s="18">
-        <f>D11/$D$16</f>
+        <f t="shared" si="0"/>
         <v>4.5694302004602727E-3</v>
       </c>
     </row>
@@ -776,7 +776,7 @@
         <v>0.71336513619694197</v>
       </c>
       <c r="E12" s="18">
-        <f>D12/$D$16</f>
+        <f t="shared" si="0"/>
         <v>5.706503096220922E-5</v>
       </c>
     </row>
@@ -794,7 +794,7 @@
         <v>34.702112255227497</v>
       </c>
       <c r="E13" s="18">
-        <f>D13/$D$16</f>
+        <f t="shared" si="0"/>
         <v>2.775965644824999E-3</v>
       </c>
     </row>
@@ -812,7 +812,7 @@
         <v>7.8544585529197599</v>
       </c>
       <c r="E14" s="18">
-        <f>D14/$D$16</f>
+        <f t="shared" si="0"/>
         <v>6.2831066135816092E-4</v>
       </c>
     </row>
@@ -830,7 +830,7 @@
         <v>86.745287071513303</v>
       </c>
       <c r="E15" s="18">
-        <f>D15/$D$16</f>
+        <f t="shared" si="0"/>
         <v>6.9391146852949524E-3</v>
       </c>
     </row>
@@ -848,7 +848,7 @@
         <v>12500.9156074823</v>
       </c>
       <c r="E16" s="18">
-        <f>D16/$D$16</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
